--- a/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_4_dbs.xlsx
+++ b/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_4_dbs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -392,7 +392,6 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,26 +665,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="23.5" customWidth="1" style="58" min="1" max="1"/>
-    <col width="19.875" customWidth="1" style="58" min="2" max="2"/>
-    <col width="47.5" customWidth="1" style="58" min="3" max="3"/>
-    <col width="47.375" customWidth="1" style="58" min="4" max="4"/>
-    <col width="12.625" customWidth="1" style="58" min="5" max="5"/>
-    <col width="16.875" customWidth="1" style="58" min="6" max="6"/>
-    <col width="29.5" customWidth="1" style="58" min="7" max="7"/>
-    <col width="49.375" customWidth="1" style="9" min="8" max="8"/>
-    <col width="40.875" customWidth="1" style="58" min="9" max="9"/>
-    <col width="9.75" customWidth="1" style="58" min="10" max="10"/>
-    <col width="35.375" customWidth="1" style="58" min="11" max="11"/>
-    <col width="13.875" customWidth="1" style="58" min="12" max="12"/>
-    <col width="36.625" customWidth="1" style="58" min="13" max="13"/>
-    <col width="11" customWidth="1" style="58" min="14" max="14"/>
-    <col width="11.375" bestFit="1" customWidth="1" style="58" min="15" max="15"/>
-    <col width="11.75" bestFit="1" customWidth="1" style="58" min="16" max="16"/>
-    <col width="22.125" bestFit="1" customWidth="1" style="58" min="17" max="20"/>
-    <col width="11" customWidth="1" style="58" min="21" max="16384"/>
+    <col width="23.5" customWidth="1" style="8" min="1" max="1"/>
+    <col width="19.83203125" customWidth="1" style="8" min="2" max="2"/>
+    <col width="47.5" customWidth="1" style="8" min="3" max="3"/>
+    <col width="47.33203125" customWidth="1" style="8" min="4" max="4"/>
+    <col width="12.58203125" customWidth="1" style="8" min="5" max="5"/>
+    <col width="16.83203125" customWidth="1" style="8" min="6" max="6"/>
+    <col width="29.5" customWidth="1" style="8" min="7" max="7"/>
+    <col width="49.33203125" customWidth="1" style="9" min="8" max="8"/>
+    <col width="40.83203125" customWidth="1" style="8" min="9" max="9"/>
+    <col width="9.75" customWidth="1" style="8" min="10" max="10"/>
+    <col width="35.33203125" customWidth="1" style="8" min="11" max="11"/>
+    <col width="13.83203125" customWidth="1" style="8" min="12" max="12"/>
+    <col width="36.58203125" customWidth="1" style="8" min="13" max="13"/>
+    <col width="11" customWidth="1" style="8" min="14" max="14"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="8" min="15" max="15"/>
+    <col width="11.75" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
+    <col width="22.08203125" bestFit="1" customWidth="1" style="8" min="17" max="20"/>
+    <col width="11" customWidth="1" style="8" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -795,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="56.25" customFormat="1" customHeight="1" s="6">
+    <row r="2" ht="55.5" customFormat="1" customHeight="1" s="6">
       <c r="A2" s="16" t="inlineStr">
         <is>
           <t>select_one recorder_list</t>
@@ -837,7 +836,7 @@
       <c r="S2" s="18" t="n"/>
       <c r="T2" s="18" t="n"/>
     </row>
-    <row r="3" ht="18.75" customFormat="1" customHeight="1" s="6">
+    <row r="3" ht="18.5" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>string</t>
@@ -879,7 +878,7 @@
       <c r="S3" s="18" t="n"/>
       <c r="T3" s="18" t="n"/>
     </row>
-    <row r="4" ht="18.75" customFormat="1" customHeight="1" s="6">
+    <row r="4" ht="18.5" customFormat="1" customHeight="1" s="6">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>string</t>
@@ -925,7 +924,7 @@
       <c r="S4" s="18" t="n"/>
       <c r="T4" s="18" t="n"/>
     </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="6">
+    <row r="5" ht="18.5" customFormat="1" customHeight="1" s="6">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>string</t>
@@ -971,7 +970,7 @@
       <c r="S5" s="18" t="n"/>
       <c r="T5" s="18" t="n"/>
     </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="6">
+    <row r="6" ht="18.5" customFormat="1" customHeight="1" s="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>string</t>
@@ -1017,7 +1016,7 @@
       </c>
       <c r="T6" s="18" t="n"/>
     </row>
-    <row r="7" ht="18.75" customFormat="1" customHeight="1" s="6">
+    <row r="7" ht="18.5" customFormat="1" customHeight="1" s="6">
       <c r="A7" s="16" t="n"/>
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="17" t="n"/>
@@ -1039,7 +1038,7 @@
       <c r="S7" s="18" t="n"/>
       <c r="T7" s="18" t="n"/>
     </row>
-    <row r="8" ht="75" customFormat="1" customHeight="1" s="6">
+    <row r="8" ht="74" customFormat="1" customHeight="1" s="6">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>select_one id_type</t>
@@ -1077,7 +1076,7 @@
       <c r="S8" s="18" t="n"/>
       <c r="T8" s="18" t="n"/>
     </row>
-    <row r="9" ht="112.5" customFormat="1" customHeight="1" s="6">
+    <row r="9" ht="111" customFormat="1" customHeight="1" s="6">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>select_one warning_note</t>
@@ -1115,7 +1114,7 @@
       <c r="S9" s="18" t="n"/>
       <c r="T9" s="18" t="n"/>
     </row>
-    <row r="10" ht="18.75" customFormat="1" customHeight="1" s="6">
+    <row r="10" ht="18.5" customFormat="1" customHeight="1" s="6">
       <c r="A10" s="20" t="n"/>
       <c r="B10" s="20" t="n"/>
       <c r="C10" s="21" t="n"/>
@@ -1247,7 +1246,7 @@
       <c r="S13" s="27" t="n"/>
       <c r="T13" s="27" t="n"/>
     </row>
-    <row r="14" ht="31.5" customFormat="1" customHeight="1" s="3">
+    <row r="14" customFormat="1" s="3">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1307,7 +1306,7 @@
       <c r="S15" s="37" t="n"/>
       <c r="T15" s="37" t="n"/>
     </row>
-    <row r="16" ht="31.5" customFormat="1" customHeight="1" s="6">
+    <row r="16" ht="31" customFormat="1" customHeight="1" s="6">
       <c r="A16" s="47" t="inlineStr">
         <is>
           <t>string</t>
@@ -1501,7 +1500,7 @@
       <c r="S20" s="18" t="n"/>
       <c r="T20" s="18" t="n"/>
     </row>
-    <row r="21" ht="31.5" customFormat="1" customHeight="1" s="6">
+    <row r="21" ht="31" customFormat="1" customHeight="1" s="6">
       <c r="A21" s="52" t="inlineStr">
         <is>
           <t>text</t>
@@ -1662,7 +1661,7 @@
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>9. Température de la pièce (°c)</t>
+          <t>9. Température in degrees (°c)</t>
         </is>
       </c>
       <c r="D25" s="42" t="n"/>
@@ -1700,7 +1699,7 @@
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>11. Date et heure d'élution</t>
+          <t>11. Date of start</t>
         </is>
       </c>
       <c r="D26" s="42" t="n"/>
@@ -1738,7 +1737,7 @@
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
-          <t>12. Veuiller entrer le numéro du lot OV16</t>
+          <t>12. Lot Number for OV16</t>
         </is>
       </c>
       <c r="D27" s="42" t="n"/>
@@ -1776,7 +1775,7 @@
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>13. Résultat de la 1ère lecture (Une heure)</t>
+          <t>13. Results</t>
         </is>
       </c>
       <c r="D28" s="42" t="inlineStr">
@@ -1978,7 +1977,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="63" customFormat="1" customHeight="1" s="6">
+    <row r="33" ht="62" customFormat="1" customHeight="1" s="6">
       <c r="A33" s="18" t="inlineStr">
         <is>
           <t>note</t>
@@ -2234,7 +2233,7 @@
       <c r="S38" s="18" t="n"/>
       <c r="T38" s="18" t="n"/>
     </row>
-    <row r="39" ht="31.5" customFormat="1" customHeight="1" s="6">
+    <row r="39" ht="31" customFormat="1" customHeight="1" s="6">
       <c r="A39" s="18" t="inlineStr">
         <is>
           <t>image</t>
@@ -2517,14 +2516,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="16.375" customWidth="1" style="58" min="1" max="1"/>
-    <col width="49.5" bestFit="1" customWidth="1" style="58" min="2" max="2"/>
-    <col width="36.125" customWidth="1" style="58" min="3" max="3"/>
-    <col width="11" customWidth="1" style="58" min="4" max="4"/>
-    <col width="17.625" bestFit="1" customWidth="1" style="58" min="5" max="5"/>
-    <col width="11" customWidth="1" style="58" min="6" max="16384"/>
+    <col width="16.33203125" customWidth="1" style="8" min="1" max="1"/>
+    <col width="49.5" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="36.08203125" customWidth="1" style="8" min="3" max="3"/>
+    <col width="11" customWidth="1" style="8" min="4" max="4"/>
+    <col width="17.58203125" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="11" customWidth="1" style="8" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2565,12 +2564,12 @@
           <t>yes_no</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C2" s="58" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2582,36 +2581,36 @@
           <t>yes_no</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C3" s="58" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>id_type</t>
         </is>
       </c>
-      <c r="B4" s="58" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>ID_generation</t>
         </is>
       </c>
-      <c r="C4" s="58" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>ID Codes generated (from the participant form)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>id_type</t>
         </is>
@@ -2628,304 +2627,304 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>barcode_method</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>QRScann</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Scan the QR/barcode using the device</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>barcode_method</t>
         </is>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>QRManual</t>
         </is>
       </c>
-      <c r="C7" s="58" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Manual entry (if scanner fails)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>results_list</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>results_list</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Negative </t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>results_list</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Absence.de.ligne.témoin/contrôle</t>
         </is>
       </c>
-      <c r="C11" s="58" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Absence of control line</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Ligne.témoin.discontinue/partielle</t>
         </is>
       </c>
-      <c r="C12" s="58" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Discontinuous/partial control line</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Difficulté.d.absorption.d.échantillon</t>
         </is>
       </c>
-      <c r="C13" s="58" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Difficulty with sample absorption</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Difficulté.de.migration.d.échantillon</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Difficulty with sample migration</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Trace.de.solution.éludé</t>
         </is>
       </c>
-      <c r="C15" s="58" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Trace of eluded solution</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Insuffisance.du.volume.de.la.solution.éludé.dû.à.la.pipette</t>
         </is>
       </c>
-      <c r="C16" s="58" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Insufficient volume of eluded solution due to pipetting</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B17" s="58" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C17" s="58" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Other (explain)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="C19" s="58" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="C20" s="58" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="C21" s="58" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B22" s="58" t="n">
+      <c r="B22" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="C22" s="58" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>99 (For testing and training only)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>warning_note</t>
         </is>
       </c>
-      <c r="B23" s="58" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Understood</t>
         </is>
       </c>
-      <c r="C23" s="58" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>I have read and understood</t>
         </is>
@@ -2944,11 +2943,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="44.125" customWidth="1" style="58" min="1" max="1"/>
-    <col width="28.5" customWidth="1" style="58" min="2" max="2"/>
-    <col width="11" customWidth="1" style="58" min="3" max="16384"/>
+    <col width="44.08203125" customWidth="1" style="8" min="1" max="1"/>
+    <col width="28.5" customWidth="1" style="8" min="2" max="2"/>
+    <col width="11" customWidth="1" style="8" min="3" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2971,15 +2970,15 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>(Demo) 4. ITAS LF-ONCHO OV16 Results Form</t>
-        </is>
-      </c>
-      <c r="B2" s="58" t="inlineStr">
+          <t>(Uganda) 4. ITAS LF-ONCHO OV16 Results Form</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>demo_lf_itas_9999_4_dbs</t>
         </is>
       </c>
-      <c r="C2" s="58" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>English (en)</t>
         </is>
